--- a/data/trans_dic/P19-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,26; 36,12</t>
+          <t>27,72; 36,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,63; 40,05</t>
+          <t>30,81; 40,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 39,43</t>
+          <t>30,26; 39,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,59; 41,43</t>
+          <t>32,79; 41,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,78; 46,34</t>
+          <t>35,33; 46,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 43,76</t>
+          <t>32,15; 43,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,55; 47,29</t>
+          <t>36,55; 46,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 49,93</t>
+          <t>41,67; 49,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,19; 39,03</t>
+          <t>31,66; 38,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,56; 40,11</t>
+          <t>32,63; 40,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,5; 41,77</t>
+          <t>34,78; 41,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 44,3</t>
+          <t>38,1; 44,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 36,5</t>
+          <t>26,52; 36,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,42; 38,55</t>
+          <t>27,97; 38,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,39; 36,97</t>
+          <t>27,12; 37,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,14; 35,22</t>
+          <t>26,58; 34,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,27; 45,03</t>
+          <t>34,63; 45,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,54; 46,15</t>
+          <t>35,15; 46,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,33; 47,6</t>
+          <t>37,32; 47,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,16; 46,67</t>
+          <t>38,01; 46,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,86; 39,31</t>
+          <t>31,98; 39,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,99; 40,54</t>
+          <t>33,01; 40,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,73; 40,39</t>
+          <t>33,58; 40,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,97; 39,31</t>
+          <t>32,97; 39,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 28,51</t>
+          <t>21,06; 28,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 24,81</t>
+          <t>18,15; 24,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 30,96</t>
+          <t>22,97; 31,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 31,53</t>
+          <t>7,94; 32,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,6; 37,9</t>
+          <t>23,44; 37,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,09; 42,6</t>
+          <t>30,46; 43,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,73; 42,4</t>
+          <t>27,63; 42,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,55; 36,93</t>
+          <t>25,81; 37,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 29,12</t>
+          <t>22,9; 29,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,72; 28,76</t>
+          <t>22,56; 29,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,4; 32,58</t>
+          <t>25,52; 32,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 32,07</t>
+          <t>7,74; 31,49</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,38; 24,9</t>
+          <t>20,07; 24,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 21,42</t>
+          <t>16,45; 21,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 29,09</t>
+          <t>24,02; 29,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 25,03</t>
+          <t>19,22; 24,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,73; 36,26</t>
+          <t>28,65; 35,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 31,07</t>
+          <t>24,56; 31,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,12; 38,58</t>
+          <t>31,89; 38,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,94; 36,85</t>
+          <t>15,51; 36,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 28,12</t>
+          <t>24,08; 28,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,51; 24,48</t>
+          <t>20,62; 24,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 32,29</t>
+          <t>28,1; 32,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 28,68</t>
+          <t>15,75; 28,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,71; 22,82</t>
+          <t>14,82; 22,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,02; 24,27</t>
+          <t>17,01; 24,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 27,94</t>
+          <t>20,67; 27,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,72; 23,89</t>
+          <t>15,08; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,59; 34,23</t>
+          <t>26,5; 34,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,02; 32,18</t>
+          <t>25,52; 32,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,53; 34,27</t>
+          <t>27,43; 34,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,69; 33,26</t>
+          <t>17,99; 32,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,3; 28,92</t>
+          <t>22,98; 28,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,08; 28,02</t>
+          <t>23,03; 28,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,32; 30,18</t>
+          <t>25,4; 30,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,71; 28,79</t>
+          <t>18,43; 28,31</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,88</t>
+          <t>19,32; 29,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,09; 39,23</t>
+          <t>28,05; 39,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,24; 47,78</t>
+          <t>35,74; 47,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,83; 41,81</t>
+          <t>21,62; 42,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,24; 28,95</t>
+          <t>24,21; 28,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,94; 29,5</t>
+          <t>23,87; 29,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,6; 34,64</t>
+          <t>28,61; 34,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,63; 25,63</t>
+          <t>19,94; 25,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,76; 27,99</t>
+          <t>23,59; 28,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,67; 31,04</t>
+          <t>25,5; 30,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,91; 36,3</t>
+          <t>30,84; 35,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,5; 28,45</t>
+          <t>21,66; 28,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,29; 26,38</t>
+          <t>23,28; 26,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,09; 26,19</t>
+          <t>23,07; 26,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,67</t>
+          <t>27,41; 30,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,31; 27,82</t>
+          <t>18,79; 27,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,84; 33,05</t>
+          <t>29,71; 32,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,85; 32,03</t>
+          <t>28,85; 31,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,04; 36,12</t>
+          <t>33,09; 36,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 32,67</t>
+          <t>24,65; 32,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,03; 29,27</t>
+          <t>27,05; 29,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,46; 28,67</t>
+          <t>26,43; 28,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,87; 33,08</t>
+          <t>30,62; 32,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,87; 29,86</t>
+          <t>23,51; 29,66</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>129169; 171138</t>
+          <t>131350; 172995</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>133939; 175084</t>
+          <t>134698; 179070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130540; 169197</t>
+          <t>129853; 170113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163081; 207322</t>
+          <t>164127; 209883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109743; 142118</t>
+          <t>108353; 143005</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>101865; 137599</t>
+          <t>101082; 137370</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>126835; 164131</t>
+          <t>126857; 162915</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>187878; 223111</t>
+          <t>186182; 221813</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>251237; 304586</t>
+          <t>247121; 303172</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>244778; 301521</t>
+          <t>245240; 301806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>267792; 324169</t>
+          <t>269957; 324922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>360676; 419685</t>
+          <t>360948; 418500</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95627; 133945</t>
+          <t>97309; 133289</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>119019; 161453</t>
+          <t>117124; 160694</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103338; 139447</t>
+          <t>102319; 139675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117572; 158410</t>
+          <t>119551; 157200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>131173; 167440</t>
+          <t>128777; 167399</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>116421; 155548</t>
+          <t>118481; 156572</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>138980; 177199</t>
+          <t>138942; 176910</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>144640; 176901</t>
+          <t>144076; 177562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>235369; 290456</t>
+          <t>236293; 288850</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249354; 306435</t>
+          <t>249519; 305452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252825; 302700</t>
+          <t>251649; 305498</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>273287; 325792</t>
+          <t>273246; 323783</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114821; 154619</t>
+          <t>114234; 154510</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>114286; 155524</t>
+          <t>113795; 156276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121055; 161606</t>
+          <t>119861; 162433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43825; 210025</t>
+          <t>52905; 216014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39602; 63592</t>
+          <t>39335; 62719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80862; 110803</t>
+          <t>79223; 111964</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44403; 70441</t>
+          <t>45893; 70061</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42492; 61406</t>
+          <t>42919; 62840</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161721; 206775</t>
+          <t>162601; 206424</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201517; 255095</t>
+          <t>200142; 257374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174765; 224153</t>
+          <t>175600; 225732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74837; 266946</t>
+          <t>64392; 262125</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>252142; 308134</t>
+          <t>248367; 307118</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192304; 248215</t>
+          <t>190685; 247241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>272406; 334408</t>
+          <t>276175; 335201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201655; 257566</t>
+          <t>197812; 256016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>205205; 259013</t>
+          <t>204608; 254436</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>185892; 238212</t>
+          <t>188262; 239050</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>265287; 318649</t>
+          <t>263376; 320731</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>145383; 358658</t>
+          <t>150974; 354480</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>467728; 548736</t>
+          <t>470048; 550725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>394977; 471477</t>
+          <t>397061; 471041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>552524; 637877</t>
+          <t>555046; 638352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>358894; 574264</t>
+          <t>315454; 572541</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51582; 79990</t>
+          <t>51940; 79779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86912; 123938</t>
+          <t>86847; 123780</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128579; 173412</t>
+          <t>128280; 172662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69463; 112724</t>
+          <t>71125; 111321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>151248; 194667</t>
+          <t>150711; 197888</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>190570; 245035</t>
+          <t>194316; 244080</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>203232; 252964</t>
+          <t>202489; 252508</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>155283; 276328</t>
+          <t>149437; 267453</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>214239; 265826</t>
+          <t>211223; 262885</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>293594; 356417</t>
+          <t>292978; 358067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>344103; 410071</t>
+          <t>345209; 412080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>243717; 375047</t>
+          <t>240097; 368756</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57869; 86114</t>
+          <t>57620; 86783</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74956; 104699</t>
+          <t>74849; 106420</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104073; 137202</t>
+          <t>102637; 136796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52279; 100096</t>
+          <t>51770; 102628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>302463; 361307</t>
+          <t>302138; 361562</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>265593; 327307</t>
+          <t>264791; 323491</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>309450; 374861</t>
+          <t>309516; 374324</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>147326; 192320</t>
+          <t>149670; 193766</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>367280; 432800</t>
+          <t>364654; 434502</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>353301; 427248</t>
+          <t>350892; 421698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>423210; 497070</t>
+          <t>422259; 492570</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>212866; 281594</t>
+          <t>214378; 280324</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>761446; 862448</t>
+          <t>760983; 861321</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>789550; 895597</t>
+          <t>788848; 889403</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>932389; 1038567</t>
+          <t>928138; 1034334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>648106; 933704</t>
+          <t>630880; 928120</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1007923; 1116332</t>
+          <t>1003473; 1109676</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1023772; 1136633</t>
+          <t>1024076; 1134406</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1166928; 1275448</t>
+          <t>1168642; 1280684</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>825161; 1158844</t>
+          <t>874242; 1169247</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1796375; 1945408</t>
+          <t>1797629; 1944819</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1843983; 1997615</t>
+          <t>1841524; 1998242</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2135411; 2288053</t>
+          <t>2118211; 2280941</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1647763; 2061292</t>
+          <t>1623178; 2047440</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 36,51</t>
+          <t>27,27; 36,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 40,96</t>
+          <t>30,55; 40,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,26; 39,64</t>
+          <t>29,97; 39,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,79; 41,94</t>
+          <t>33,49; 42,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 46,63</t>
+          <t>35,42; 46,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 43,69</t>
+          <t>32,65; 44,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,55; 46,94</t>
+          <t>36,81; 47,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,67; 49,64</t>
+          <t>41,0; 49,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,66; 38,85</t>
+          <t>32,1; 38,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,63; 40,15</t>
+          <t>32,82; 40,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,78; 41,86</t>
+          <t>34,42; 41,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,1; 44,18</t>
+          <t>38,19; 44,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,52; 36,33</t>
+          <t>26,12; 36,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,97; 38,37</t>
+          <t>28,41; 37,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 37,03</t>
+          <t>27,17; 37,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 34,95</t>
+          <t>25,8; 34,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,63; 45,02</t>
+          <t>34,31; 44,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,15; 46,45</t>
+          <t>35,08; 46,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,32; 47,52</t>
+          <t>36,8; 47,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 46,85</t>
+          <t>38,19; 46,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,98; 39,1</t>
+          <t>32,63; 39,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 40,41</t>
+          <t>32,49; 40,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,76</t>
+          <t>33,31; 41,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,97; 39,07</t>
+          <t>32,54; 38,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 28,49</t>
+          <t>20,66; 28,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,93</t>
+          <t>18,42; 24,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,97; 31,12</t>
+          <t>23,06; 30,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 32,43</t>
+          <t>26,33; 35,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,44; 37,38</t>
+          <t>23,88; 38,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,46; 43,04</t>
+          <t>30,69; 42,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,63; 42,17</t>
+          <t>27,09; 42,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,81; 37,79</t>
+          <t>26,19; 37,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,9; 29,07</t>
+          <t>22,62; 29,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 29,02</t>
+          <t>22,71; 29,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,52; 32,81</t>
+          <t>24,98; 32,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 31,49</t>
+          <t>27,68; 34,75</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 24,82</t>
+          <t>20,25; 25,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,45; 21,33</t>
+          <t>16,81; 21,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,02; 29,16</t>
+          <t>23,64; 29,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 24,88</t>
+          <t>19,28; 24,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,65; 35,62</t>
+          <t>28,74; 35,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,56; 31,18</t>
+          <t>24,45; 31,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 38,84</t>
+          <t>31,8; 38,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,51; 36,42</t>
+          <t>31,58; 37,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 28,22</t>
+          <t>24,21; 28,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 24,46</t>
+          <t>20,64; 24,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 32,31</t>
+          <t>28,08; 32,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 28,59</t>
+          <t>25,22; 29,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 22,76</t>
+          <t>14,64; 23,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,01; 24,24</t>
+          <t>17,04; 24,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,82</t>
+          <t>20,78; 27,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,08; 23,6</t>
+          <t>13,08; 20,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,5; 34,79</t>
+          <t>26,5; 34,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,52; 32,05</t>
+          <t>25,37; 32,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,43; 34,2</t>
+          <t>27,43; 34,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 32,19</t>
+          <t>20,45; 25,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,98; 28,6</t>
+          <t>22,89; 28,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,03; 28,15</t>
+          <t>22,77; 27,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,4; 30,32</t>
+          <t>25,34; 30,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 28,31</t>
+          <t>18,27; 22,53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,32; 29,1</t>
+          <t>19,49; 29,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,05; 39,88</t>
+          <t>28,08; 39,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,74; 47,64</t>
+          <t>35,57; 47,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 42,86</t>
+          <t>22,23; 40,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,21; 28,98</t>
+          <t>23,99; 29,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,87; 29,16</t>
+          <t>23,94; 29,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,61; 34,59</t>
+          <t>28,66; 34,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,94; 25,82</t>
+          <t>19,97; 25,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,59; 28,1</t>
+          <t>23,98; 28,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,5; 30,64</t>
+          <t>25,6; 30,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,84; 35,98</t>
+          <t>31,07; 36,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 28,32</t>
+          <t>21,43; 27,42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,28; 26,35</t>
+          <t>23,47; 26,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,07; 26,01</t>
+          <t>23,08; 26,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,41; 30,55</t>
+          <t>27,33; 30,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,79; 27,65</t>
+          <t>24,69; 28,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,71; 32,86</t>
+          <t>29,82; 33,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,85; 31,96</t>
+          <t>28,88; 31,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,09; 36,26</t>
+          <t>32,95; 36,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,65; 32,97</t>
+          <t>29,83; 32,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,05; 29,26</t>
+          <t>27,08; 29,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,43; 28,68</t>
+          <t>26,48; 28,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,62; 32,97</t>
+          <t>30,67; 32,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,51; 29,66</t>
+          <t>27,73; 29,93</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>204500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>204772</t>
+          <t>219386</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>390857</t>
+          <t>423887</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>131350; 172995</t>
+          <t>129193; 172926</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134698; 179070</t>
+          <t>133580; 176542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129853; 170113</t>
+          <t>128613; 169603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164127; 209883</t>
+          <t>182683; 230970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>108353; 143005</t>
+          <t>108619; 143203</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>101082; 137370</t>
+          <t>102674; 139100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>126857; 162915</t>
+          <t>127767; 163408</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>186182; 221813</t>
+          <t>199957; 239653</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247121; 303172</t>
+          <t>250548; 301555</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>245240; 301806</t>
+          <t>246690; 301453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>269957; 324922</t>
+          <t>267120; 324953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>360948; 418500</t>
+          <t>394514; 456547</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137084</t>
+          <t>142824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>160586</t>
+          <t>176680</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>297670</t>
+          <t>319504</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97309; 133289</t>
+          <t>95842; 133240</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117124; 160694</t>
+          <t>118997; 159070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102319; 139675</t>
+          <t>102485; 141436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119551; 157200</t>
+          <t>123948; 164524</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>128777; 167399</t>
+          <t>127573; 166778</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>118481; 156572</t>
+          <t>118243; 156559</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>138942; 176910</t>
+          <t>137006; 176041</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>144076; 177562</t>
+          <t>159786; 195780</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236293; 288850</t>
+          <t>241096; 292526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249519; 305452</t>
+          <t>245569; 304381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251649; 305498</t>
+          <t>249628; 307903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>273246; 323783</t>
+          <t>292507; 348736</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128788</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>201940</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114234; 154510</t>
+          <t>112071; 152865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113795; 156276</t>
+          <t>115471; 156142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119861; 162433</t>
+          <t>120340; 160673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52905; 216014</t>
+          <t>123522; 167060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39335; 62719</t>
+          <t>40066; 64946</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79223; 111964</t>
+          <t>79833; 110945</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45893; 70061</t>
+          <t>45000; 70367</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42919; 62840</t>
+          <t>48930; 70693</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162601; 206424</t>
+          <t>160661; 208728</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200142; 257374</t>
+          <t>201457; 258550</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175600; 225732</t>
+          <t>171856; 222196</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64392; 262125</t>
+          <t>181585; 227957</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226032</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>274117</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>500148</t>
+          <t>540250</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>248367; 307118</t>
+          <t>250626; 309619</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>190685; 247241</t>
+          <t>194801; 246282</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>276175; 335201</t>
+          <t>271783; 333735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197812; 256016</t>
+          <t>216751; 274808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>204608; 254436</t>
+          <t>205318; 255981</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>188262; 239050</t>
+          <t>187458; 237899</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>263376; 320731</t>
+          <t>262597; 317926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>150974; 354480</t>
+          <t>270226; 316655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>470048; 550725</t>
+          <t>472582; 550500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>397061; 471041</t>
+          <t>397477; 469495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>555046; 638352</t>
+          <t>554641; 636458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>315454; 572541</t>
+          <t>499304; 582614</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>93004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>200251</t>
+          <t>187952</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>290345</t>
+          <t>280956</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51940; 79779</t>
+          <t>51338; 80788</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86847; 123780</t>
+          <t>86983; 123701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128280; 172662</t>
+          <t>128987; 171882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71125; 111321</t>
+          <t>73836; 113636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>150711; 197888</t>
+          <t>150703; 195764</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>194316; 244080</t>
+          <t>193209; 244850</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>202489; 252508</t>
+          <t>202465; 253195</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>149437; 267453</t>
+          <t>167916; 209536</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>211223; 262885</t>
+          <t>210426; 263998</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>292978; 358067</t>
+          <t>289644; 354992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345209; 412080</t>
+          <t>344425; 409983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>240097; 368756</t>
+          <t>253088; 312094</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75466</t>
+          <t>72414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>169111</t>
+          <t>188209</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>244577</t>
+          <t>260623</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57620; 86783</t>
+          <t>58124; 86811</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74849; 106420</t>
+          <t>74953; 106157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>102637; 136796</t>
+          <t>102126; 136266</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51770; 102628</t>
+          <t>52501; 96189</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>302138; 361562</t>
+          <t>299294; 364907</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>264791; 323491</t>
+          <t>265565; 324268</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>309516; 374324</t>
+          <t>310062; 372787</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>149670; 193766</t>
+          <t>166232; 214978</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>364654; 434502</t>
+          <t>370695; 438401</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>350892; 421698</t>
+          <t>352326; 417896</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>422259; 492570</t>
+          <t>425447; 498216</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>214378; 280324</t>
+          <t>228978; 293078</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>843550</t>
+          <t>901696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1060792</t>
+          <t>1125462</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1904342</t>
+          <t>2027159</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>760983; 861321</t>
+          <t>767221; 868321</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>788848; 889403</t>
+          <t>789280; 894593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>928138; 1034334</t>
+          <t>925395; 1034152</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>630880; 928120</t>
+          <t>844246; 960125</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1003473; 1109676</t>
+          <t>1007194; 1116436</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1024076; 1134406</t>
+          <t>1024956; 1135115</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1168642; 1280684</t>
+          <t>1163812; 1278238</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>874242; 1169247</t>
+          <t>1074566; 1174476</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1797629; 1944819</t>
+          <t>1799602; 1942398</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1841524; 1998242</t>
+          <t>1845315; 2000817</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2118211; 2280941</t>
+          <t>2121845; 2280564</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1623178; 2047440</t>
+          <t>1947424; 2101667</t>
         </is>
       </c>
     </row>
